--- a/arista_territory_chart.xlsx
+++ b/arista_territory_chart.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/tarista_my_yearupunited_org/Documents/Documents/DATA_Labs/Capstone_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="378" documentId="8_{06790B3B-F6F6-403F-8770-83E80B4391D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE6CFDFC-D2DB-4D5D-BBC0-ADF1F5BCC442}"/>
+  <xr:revisionPtr revIDLastSave="394" documentId="8_{06790B3B-F6F6-403F-8770-83E80B4391D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA2B0227-F2C4-4210-9BB7-7EC238FB03A3}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{7B7E3420-8EA8-4E0C-BBB0-5358CDC6EF63}"/>
+    <workbookView minimized="1" xWindow="1392" yWindow="2772" windowWidth="2388" windowHeight="564" activeTab="1" xr2:uid="{7B7E3420-8EA8-4E0C-BBB0-5358CDC6EF63}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="81" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -3937,7 +3937,7 @@
           </a:p>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" cap="none" spc="0">
+              <a:defRPr cap="none">
                 <a:ln w="0"/>
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
@@ -3970,7 +3970,7 @@
           </a:p>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" cap="none" spc="0">
+              <a:defRPr cap="none">
                 <a:ln w="0"/>
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
@@ -4050,52 +4050,13 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="b"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4124,6 +4085,9 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4152,6 +4116,9 @@
       <c:pivotFmt>
         <c:idx val="3"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4180,6 +4147,9 @@
       <c:pivotFmt>
         <c:idx val="4"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4208,6 +4178,9 @@
       <c:pivotFmt>
         <c:idx val="5"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4236,6 +4209,9 @@
       <c:pivotFmt>
         <c:idx val="6"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4264,6 +4240,9 @@
       <c:pivotFmt>
         <c:idx val="7"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4292,6 +4271,9 @@
       <c:pivotFmt>
         <c:idx val="8"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4320,6 +4302,9 @@
       <c:pivotFmt>
         <c:idx val="9"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4348,6 +4333,9 @@
       <c:pivotFmt>
         <c:idx val="10"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4376,6 +4364,9 @@
       <c:pivotFmt>
         <c:idx val="11"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4404,6 +4395,9 @@
       <c:pivotFmt>
         <c:idx val="12"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4432,6 +4426,9 @@
       <c:pivotFmt>
         <c:idx val="13"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4460,6 +4457,9 @@
       <c:pivotFmt>
         <c:idx val="14"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4488,6 +4488,9 @@
       <c:pivotFmt>
         <c:idx val="15"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4516,6 +4519,9 @@
       <c:pivotFmt>
         <c:idx val="16"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4544,6 +4550,9 @@
       <c:pivotFmt>
         <c:idx val="17"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4572,6 +4581,9 @@
       <c:pivotFmt>
         <c:idx val="18"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4600,6 +4612,9 @@
       <c:pivotFmt>
         <c:idx val="19"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4628,6 +4643,9 @@
       <c:pivotFmt>
         <c:idx val="20"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4656,6 +4674,9 @@
       <c:pivotFmt>
         <c:idx val="21"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4684,6 +4705,9 @@
       <c:pivotFmt>
         <c:idx val="22"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4712,6 +4736,9 @@
       <c:pivotFmt>
         <c:idx val="23"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4740,6 +4767,9 @@
       <c:pivotFmt>
         <c:idx val="24"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4768,6 +4798,9 @@
       <c:pivotFmt>
         <c:idx val="25"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4796,6 +4829,9 @@
       <c:pivotFmt>
         <c:idx val="26"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4824,6 +4860,9 @@
       <c:pivotFmt>
         <c:idx val="27"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4852,6 +4891,9 @@
       <c:pivotFmt>
         <c:idx val="28"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4880,6 +4922,9 @@
       <c:pivotFmt>
         <c:idx val="29"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4908,6 +4953,9 @@
       <c:pivotFmt>
         <c:idx val="30"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4936,6 +4984,9 @@
       <c:pivotFmt>
         <c:idx val="31"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4964,6 +5015,9 @@
       <c:pivotFmt>
         <c:idx val="32"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4992,6 +5046,9 @@
       <c:pivotFmt>
         <c:idx val="33"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5020,6 +5077,9 @@
       <c:pivotFmt>
         <c:idx val="34"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5048,6 +5108,9 @@
       <c:pivotFmt>
         <c:idx val="35"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5076,6 +5139,9 @@
       <c:pivotFmt>
         <c:idx val="36"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5104,6 +5170,9 @@
       <c:pivotFmt>
         <c:idx val="37"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5132,6 +5201,9 @@
       <c:pivotFmt>
         <c:idx val="38"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5160,6 +5232,9 @@
       <c:pivotFmt>
         <c:idx val="39"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5188,6 +5263,9 @@
       <c:pivotFmt>
         <c:idx val="40"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5216,6 +5294,9 @@
       <c:pivotFmt>
         <c:idx val="41"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5244,6 +5325,9 @@
       <c:pivotFmt>
         <c:idx val="42"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5272,6 +5356,9 @@
       <c:pivotFmt>
         <c:idx val="43"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5300,6 +5387,9 @@
       <c:pivotFmt>
         <c:idx val="44"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5328,6 +5418,9 @@
       <c:pivotFmt>
         <c:idx val="45"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5356,6 +5449,9 @@
       <c:pivotFmt>
         <c:idx val="46"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5384,6 +5480,9 @@
       <c:pivotFmt>
         <c:idx val="47"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5412,6 +5511,9 @@
       <c:pivotFmt>
         <c:idx val="48"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5440,6 +5542,9 @@
       <c:pivotFmt>
         <c:idx val="49"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5468,6 +5573,9 @@
       <c:pivotFmt>
         <c:idx val="50"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5496,6 +5604,9 @@
       <c:pivotFmt>
         <c:idx val="51"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5524,6 +5635,9 @@
       <c:pivotFmt>
         <c:idx val="52"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5552,6 +5666,9 @@
       <c:pivotFmt>
         <c:idx val="53"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5580,6 +5697,9 @@
       <c:pivotFmt>
         <c:idx val="54"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5608,6 +5728,9 @@
       <c:pivotFmt>
         <c:idx val="55"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5636,6 +5759,9 @@
       <c:pivotFmt>
         <c:idx val="56"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5664,6 +5790,9 @@
       <c:pivotFmt>
         <c:idx val="57"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5692,6 +5821,9 @@
       <c:pivotFmt>
         <c:idx val="58"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5720,6 +5852,9 @@
       <c:pivotFmt>
         <c:idx val="59"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5748,6 +5883,9 @@
       <c:pivotFmt>
         <c:idx val="60"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5776,6 +5914,9 @@
       <c:pivotFmt>
         <c:idx val="61"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5804,6 +5945,9 @@
       <c:pivotFmt>
         <c:idx val="62"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5832,6 +5976,9 @@
       <c:pivotFmt>
         <c:idx val="63"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5860,6 +6007,9 @@
       <c:pivotFmt>
         <c:idx val="64"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5888,6 +6038,9 @@
       <c:pivotFmt>
         <c:idx val="65"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5916,6 +6069,9 @@
       <c:pivotFmt>
         <c:idx val="66"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5944,6 +6100,9 @@
       <c:pivotFmt>
         <c:idx val="67"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5972,6 +6131,9 @@
       <c:pivotFmt>
         <c:idx val="68"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6000,6 +6162,9 @@
       <c:pivotFmt>
         <c:idx val="69"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6028,6 +6193,9 @@
       <c:pivotFmt>
         <c:idx val="70"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6056,6 +6224,9 @@
       <c:pivotFmt>
         <c:idx val="71"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6084,6 +6255,9 @@
       <c:pivotFmt>
         <c:idx val="72"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6112,6 +6286,9 @@
       <c:pivotFmt>
         <c:idx val="73"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6140,6 +6317,9 @@
       <c:pivotFmt>
         <c:idx val="74"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6168,6 +6348,9 @@
       <c:pivotFmt>
         <c:idx val="75"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6196,6 +6379,9 @@
       <c:pivotFmt>
         <c:idx val="76"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6224,6 +6410,9 @@
       <c:pivotFmt>
         <c:idx val="77"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6252,6 +6441,9 @@
       <c:pivotFmt>
         <c:idx val="78"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6280,6 +6472,9 @@
       <c:pivotFmt>
         <c:idx val="79"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6308,6 +6503,9 @@
       <c:pivotFmt>
         <c:idx val="80"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6336,6 +6534,9 @@
       <c:pivotFmt>
         <c:idx val="81"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6364,6 +6565,9 @@
       <c:pivotFmt>
         <c:idx val="82"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6392,6 +6596,9 @@
       <c:pivotFmt>
         <c:idx val="83"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6420,6 +6627,9 @@
       <c:pivotFmt>
         <c:idx val="84"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6448,6 +6658,9 @@
       <c:pivotFmt>
         <c:idx val="85"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6476,6 +6689,9 @@
       <c:pivotFmt>
         <c:idx val="86"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6504,6 +6720,9 @@
       <c:pivotFmt>
         <c:idx val="87"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6532,6 +6751,9 @@
       <c:pivotFmt>
         <c:idx val="88"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6560,6 +6782,9 @@
       <c:pivotFmt>
         <c:idx val="89"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6588,6 +6813,9 @@
       <c:pivotFmt>
         <c:idx val="90"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6616,6 +6844,9 @@
       <c:pivotFmt>
         <c:idx val="91"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6644,6 +6875,9 @@
       <c:pivotFmt>
         <c:idx val="92"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6672,6 +6906,9 @@
       <c:pivotFmt>
         <c:idx val="93"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6700,6 +6937,9 @@
       <c:pivotFmt>
         <c:idx val="94"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6728,6 +6968,9 @@
       <c:pivotFmt>
         <c:idx val="95"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6756,6 +6999,9 @@
       <c:pivotFmt>
         <c:idx val="96"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6784,6 +7030,9 @@
       <c:pivotFmt>
         <c:idx val="97"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6812,6 +7061,9 @@
       <c:pivotFmt>
         <c:idx val="98"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6840,6 +7092,9 @@
       <c:pivotFmt>
         <c:idx val="99"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6868,6 +7123,9 @@
       <c:pivotFmt>
         <c:idx val="100"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6896,6 +7154,9 @@
       <c:pivotFmt>
         <c:idx val="101"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6924,6 +7185,9 @@
       <c:pivotFmt>
         <c:idx val="102"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6952,6 +7216,9 @@
       <c:pivotFmt>
         <c:idx val="103"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6980,6 +7247,9 @@
       <c:pivotFmt>
         <c:idx val="104"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7008,6 +7278,9 @@
       <c:pivotFmt>
         <c:idx val="105"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7036,6 +7309,9 @@
       <c:pivotFmt>
         <c:idx val="106"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7064,6 +7340,9 @@
       <c:pivotFmt>
         <c:idx val="107"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7092,6 +7371,9 @@
       <c:pivotFmt>
         <c:idx val="108"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7120,6 +7402,9 @@
       <c:pivotFmt>
         <c:idx val="109"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7148,6 +7433,9 @@
       <c:pivotFmt>
         <c:idx val="110"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7176,6 +7464,9 @@
       <c:pivotFmt>
         <c:idx val="111"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7204,6 +7495,9 @@
       <c:pivotFmt>
         <c:idx val="112"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7232,6 +7526,9 @@
       <c:pivotFmt>
         <c:idx val="113"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7260,6 +7557,9 @@
       <c:pivotFmt>
         <c:idx val="114"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7288,6 +7588,9 @@
       <c:pivotFmt>
         <c:idx val="115"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7316,6 +7619,9 @@
       <c:pivotFmt>
         <c:idx val="116"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7344,6 +7650,9 @@
       <c:pivotFmt>
         <c:idx val="117"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7372,6 +7681,9 @@
       <c:pivotFmt>
         <c:idx val="118"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7400,6 +7712,9 @@
       <c:pivotFmt>
         <c:idx val="119"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7428,6 +7743,9 @@
       <c:pivotFmt>
         <c:idx val="120"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7456,6 +7774,9 @@
       <c:pivotFmt>
         <c:idx val="121"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7484,6 +7805,9 @@
       <c:pivotFmt>
         <c:idx val="122"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7512,6 +7836,9 @@
       <c:pivotFmt>
         <c:idx val="123"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7540,6 +7867,9 @@
       <c:pivotFmt>
         <c:idx val="124"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7568,6 +7898,9 @@
       <c:pivotFmt>
         <c:idx val="125"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7596,6 +7929,9 @@
       <c:pivotFmt>
         <c:idx val="126"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7624,6 +7960,9 @@
       <c:pivotFmt>
         <c:idx val="127"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7652,6 +7991,9 @@
       <c:pivotFmt>
         <c:idx val="128"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7680,6 +8022,9 @@
       <c:pivotFmt>
         <c:idx val="129"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7708,6 +8053,9 @@
       <c:pivotFmt>
         <c:idx val="130"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7736,6 +8084,9 @@
       <c:pivotFmt>
         <c:idx val="131"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7764,6 +8115,9 @@
       <c:pivotFmt>
         <c:idx val="132"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -7821,9 +8175,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:trendline>
             <c:spPr>
               <a:ln w="19050" cap="rnd">
@@ -8152,7 +8503,7 @@
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -8248,6 +8599,66 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Revenue</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> $</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="&quot;$&quot;#,##0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -8372,8 +8783,6 @@
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
@@ -9631,10 +10040,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="tracy arista" refreshedDate="46141.667699768521" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="49" xr:uid="{BF491BCE-F5E5-47F6-8A15-7671F3D9E947}">
   <cacheSource type="worksheet">
@@ -10409,7 +10814,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05DC4C15-B745-4B62-9C0D-6F8626F16B52}" name="PivotTable42" cacheId="81" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05DC4C15-B745-4B62-9C0D-6F8626F16B52}" name="PivotTable42" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="A3:B52" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0">
@@ -11021,10 +11426,10 @@
     <dataField name="Sum of revenue" fld="1" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="0">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
